--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119894784</v>
+        <v>119894781</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525785</v>
+        <v>525748</v>
       </c>
       <c r="R2" t="n">
-        <v>7178045</v>
+        <v>7178093</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119894781</v>
+        <v>119894783</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525748</v>
+        <v>525755</v>
       </c>
       <c r="R3" t="n">
-        <v>7178093</v>
+        <v>7178042</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119894783</v>
+        <v>119894788</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525755</v>
+        <v>525854</v>
       </c>
       <c r="R4" t="n">
-        <v>7178042</v>
+        <v>7178147</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,6 +1023,7 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1038,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119894788</v>
+        <v>119894782</v>
       </c>
       <c r="B5" t="n">
         <v>78526</v>
@@ -1081,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525854</v>
+        <v>525711</v>
       </c>
       <c r="R5" t="n">
-        <v>7178147</v>
+        <v>7178045</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1116,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1145,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119894787</v>
+        <v>119894784</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525830</v>
+        <v>525785</v>
       </c>
       <c r="R7" t="n">
-        <v>7178101</v>
+        <v>7178045</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1523,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119894782</v>
+        <v>119894787</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525711</v>
+        <v>525830</v>
       </c>
       <c r="R9" t="n">
-        <v>7178045</v>
+        <v>7178101</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119894781</v>
+        <v>119894787</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525748</v>
+        <v>525830</v>
       </c>
       <c r="R2" t="n">
-        <v>7178093</v>
+        <v>7178101</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119894783</v>
+        <v>119894786</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525755</v>
+        <v>525808</v>
       </c>
       <c r="R3" t="n">
-        <v>7178042</v>
+        <v>7178066</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119894788</v>
+        <v>119894789</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525854</v>
+        <v>525855</v>
       </c>
       <c r="R4" t="n">
-        <v>7178147</v>
+        <v>7178125</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1039,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119894782</v>
+        <v>119894783</v>
       </c>
       <c r="B5" t="n">
         <v>78526</v>
@@ -1082,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525711</v>
+        <v>525755</v>
       </c>
       <c r="R5" t="n">
-        <v>7178045</v>
+        <v>7178042</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1117,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119894789</v>
+        <v>119894782</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1203,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525855</v>
+        <v>525711</v>
       </c>
       <c r="R6" t="n">
-        <v>7178125</v>
+        <v>7178045</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119894784</v>
+        <v>119894781</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1324,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525785</v>
+        <v>525748</v>
       </c>
       <c r="R7" t="n">
-        <v>7178045</v>
+        <v>7178093</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1359,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,7 +1401,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119894786</v>
+        <v>119894788</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1445,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525808</v>
+        <v>525854</v>
       </c>
       <c r="R8" t="n">
-        <v>7178066</v>
+        <v>7178147</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1480,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,6 +1507,7 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119894787</v>
+        <v>119894784</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525830</v>
+        <v>525785</v>
       </c>
       <c r="R9" t="n">
-        <v>7178101</v>
+        <v>7178045</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119894786</v>
+        <v>119894781</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525808</v>
+        <v>525748</v>
       </c>
       <c r="R3" t="n">
-        <v>7178066</v>
+        <v>7178093</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119894789</v>
+        <v>119894784</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525855</v>
+        <v>525785</v>
       </c>
       <c r="R4" t="n">
-        <v>7178125</v>
+        <v>7178045</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119894783</v>
+        <v>119894789</v>
       </c>
       <c r="B5" t="n">
         <v>78526</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525755</v>
+        <v>525855</v>
       </c>
       <c r="R5" t="n">
-        <v>7178042</v>
+        <v>7178125</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119894782</v>
+        <v>119894786</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525711</v>
+        <v>525808</v>
       </c>
       <c r="R6" t="n">
-        <v>7178045</v>
+        <v>7178066</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119894781</v>
+        <v>119894788</v>
       </c>
       <c r="B7" t="n">
         <v>78526</v>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525748</v>
+        <v>525854</v>
       </c>
       <c r="R7" t="n">
-        <v>7178093</v>
+        <v>7178147</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,6 +1386,7 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1401,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119894788</v>
+        <v>119894782</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1444,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525854</v>
+        <v>525711</v>
       </c>
       <c r="R8" t="n">
-        <v>7178147</v>
+        <v>7178045</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1479,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,7 +1508,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119894784</v>
+        <v>119894783</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525785</v>
+        <v>525755</v>
       </c>
       <c r="R9" t="n">
-        <v>7178045</v>
+        <v>7178042</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119894787</v>
+        <v>119894789</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525830</v>
+        <v>525855</v>
       </c>
       <c r="R2" t="n">
-        <v>7178101</v>
+        <v>7178125</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
         <v>119894781</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119894784</v>
+        <v>119894782</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525785</v>
+        <v>525711</v>
       </c>
       <c r="R4" t="n">
         <v>7178045</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119894789</v>
+        <v>119894783</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525855</v>
+        <v>525755</v>
       </c>
       <c r="R5" t="n">
-        <v>7178125</v>
+        <v>7178042</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119894786</v>
+        <v>119894784</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525808</v>
+        <v>525785</v>
       </c>
       <c r="R6" t="n">
-        <v>7178066</v>
+        <v>7178045</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119894788</v>
+        <v>119894786</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525854</v>
+        <v>525808</v>
       </c>
       <c r="R7" t="n">
-        <v>7178147</v>
+        <v>7178066</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,7 +1386,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1402,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119894782</v>
+        <v>119894787</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1445,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525711</v>
+        <v>525830</v>
       </c>
       <c r="R8" t="n">
-        <v>7178045</v>
+        <v>7178101</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1480,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1522,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119894783</v>
+        <v>119894788</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525755</v>
+        <v>525854</v>
       </c>
       <c r="R9" t="n">
-        <v>7178042</v>
+        <v>7178147</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1601,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,6 +1628,7 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119894789</v>
+        <v>119894783</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525855</v>
+        <v>525755</v>
       </c>
       <c r="R2" t="n">
-        <v>7178125</v>
+        <v>7178042</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119894781</v>
+        <v>119894789</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525748</v>
+        <v>525855</v>
       </c>
       <c r="R3" t="n">
-        <v>7178093</v>
+        <v>7178125</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119894782</v>
+        <v>119894786</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525711</v>
+        <v>525808</v>
       </c>
       <c r="R4" t="n">
-        <v>7178045</v>
+        <v>7178066</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119894783</v>
+        <v>119894784</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525755</v>
+        <v>525785</v>
       </c>
       <c r="R5" t="n">
-        <v>7178042</v>
+        <v>7178045</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119894784</v>
+        <v>119894788</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525785</v>
+        <v>525854</v>
       </c>
       <c r="R6" t="n">
-        <v>7178045</v>
+        <v>7178147</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1265,7 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1280,7 +1281,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119894786</v>
+        <v>119894781</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525808</v>
+        <v>525748</v>
       </c>
       <c r="R7" t="n">
-        <v>7178066</v>
+        <v>7178093</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1358,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1522,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119894788</v>
+        <v>119894782</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1565,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525854</v>
+        <v>525711</v>
       </c>
       <c r="R9" t="n">
-        <v>7178147</v>
+        <v>7178045</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1600,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,7 +1629,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119894789</v>
+        <v>119894786</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525855</v>
+        <v>525808</v>
       </c>
       <c r="R3" t="n">
-        <v>7178125</v>
+        <v>7178066</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119894786</v>
+        <v>119894787</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525808</v>
+        <v>525830</v>
       </c>
       <c r="R4" t="n">
-        <v>7178066</v>
+        <v>7178101</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119894788</v>
+        <v>119894789</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525854</v>
+        <v>525855</v>
       </c>
       <c r="R6" t="n">
-        <v>7178147</v>
+        <v>7178125</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1265,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1402,7 +1401,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119894787</v>
+        <v>119894788</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1445,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525830</v>
+        <v>525854</v>
       </c>
       <c r="R8" t="n">
-        <v>7178101</v>
+        <v>7178147</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1480,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,6 +1507,7 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119894783</v>
+        <v>119894781</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525755</v>
+        <v>525748</v>
       </c>
       <c r="R2" t="n">
-        <v>7178042</v>
+        <v>7178093</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119894786</v>
+        <v>119894787</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525808</v>
+        <v>525830</v>
       </c>
       <c r="R3" t="n">
-        <v>7178066</v>
+        <v>7178101</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119894787</v>
+        <v>119894786</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525830</v>
+        <v>525808</v>
       </c>
       <c r="R4" t="n">
-        <v>7178101</v>
+        <v>7178066</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119894784</v>
+        <v>119894783</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525785</v>
+        <v>525755</v>
       </c>
       <c r="R5" t="n">
-        <v>7178045</v>
+        <v>7178042</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119894789</v>
+        <v>119894782</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525855</v>
+        <v>525711</v>
       </c>
       <c r="R6" t="n">
-        <v>7178125</v>
+        <v>7178045</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119894781</v>
+        <v>119894789</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525748</v>
+        <v>525855</v>
       </c>
       <c r="R7" t="n">
-        <v>7178093</v>
+        <v>7178125</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1523,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119894782</v>
+        <v>119894784</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525711</v>
+        <v>525785</v>
       </c>
       <c r="R9" t="n">
         <v>7178045</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119894781</v>
+        <v>119894784</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525748</v>
+        <v>525785</v>
       </c>
       <c r="R2" t="n">
-        <v>7178093</v>
+        <v>7178045</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119894787</v>
+        <v>119894789</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525830</v>
+        <v>525855</v>
       </c>
       <c r="R3" t="n">
-        <v>7178101</v>
+        <v>7178125</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119894782</v>
+        <v>119894788</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525711</v>
+        <v>525854</v>
       </c>
       <c r="R6" t="n">
-        <v>7178045</v>
+        <v>7178147</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1265,7 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1280,7 +1281,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119894789</v>
+        <v>119894787</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1323,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525855</v>
+        <v>525830</v>
       </c>
       <c r="R7" t="n">
-        <v>7178125</v>
+        <v>7178101</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1358,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119894788</v>
+        <v>119894781</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1444,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525854</v>
+        <v>525748</v>
       </c>
       <c r="R8" t="n">
-        <v>7178147</v>
+        <v>7178093</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1479,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1489,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,7 +1508,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119894784</v>
+        <v>119894782</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525785</v>
+        <v>525711</v>
       </c>
       <c r="R9" t="n">
         <v>7178045</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119894784</v>
+        <v>119894781</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525785</v>
+        <v>525748</v>
       </c>
       <c r="R2" t="n">
-        <v>7178045</v>
+        <v>7178093</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,19 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119894789</v>
+        <v>119894782</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525855</v>
+        <v>525711</v>
       </c>
       <c r="R3" t="n">
-        <v>7178125</v>
+        <v>7178045</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,19 +907,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119894786</v>
+        <v>119894783</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -960,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525808</v>
+        <v>525755</v>
       </c>
       <c r="R4" t="n">
-        <v>7178066</v>
+        <v>7178042</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,19 +1023,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119894783</v>
+        <v>119894784</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1081,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525755</v>
+        <v>525785</v>
       </c>
       <c r="R5" t="n">
-        <v>7178042</v>
+        <v>7178045</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1116,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,19 +1139,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119894788</v>
+        <v>119894786</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1202,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525854</v>
+        <v>525808</v>
       </c>
       <c r="R6" t="n">
-        <v>7178147</v>
+        <v>7178066</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1237,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1240,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1284,16 +1258,11 @@
         <v>119894787</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1402,19 +1371,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119894781</v>
+        <v>119894788</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1445,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525748</v>
+        <v>525854</v>
       </c>
       <c r="R8" t="n">
-        <v>7178093</v>
+        <v>7178147</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1480,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,6 +1472,7 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1523,19 +1488,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119894782</v>
+        <v>119894789</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1566,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525711</v>
+        <v>525855</v>
       </c>
       <c r="R9" t="n">
-        <v>7178045</v>
+        <v>7178125</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1601,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36318-2024 artfynd.xlsx
+++ b/artfynd/A 36318-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894782</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894786</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894787</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894788</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1601,8 +1641,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119894789</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>